--- a/healthcare_surveys/002_public_health_information_credibility_survey--healthcare_surveys.xlsx
+++ b/healthcare_surveys/002_public_health_information_credibility_survey--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>somewhat</t>
+          <t>very</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Somewhat</t>
+          <t>Very</t>
         </is>
       </c>
     </row>
@@ -961,29 +961,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>very</t>
+          <t>extremely</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Very</t>
+          <t>Extremely</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>how_confident_choices</t>
+          <t>information_type_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>extremely</t>
+          <t>health_news</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Extremely</t>
+          <t>Health News</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>health_news</t>
+          <t>health_information</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Health News</t>
+          <t>Health Information</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>health_information</t>
+          <t>medical_literature</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Health Information</t>
+          <t>Medical Literature</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>medical_literature</t>
+          <t>social_media</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Medical Literature</t>
+          <t>Social Media</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>social_media</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Social Media</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>online_search</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Online Search</t>
         </is>
       </c>
     </row>
@@ -1080,29 +1080,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>online_search</t>
+          <t>healthcare_professional</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Online Search</t>
+          <t>Healthcare Professional</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>information_type_choices</t>
+          <t>trust_level_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>healthcare_professional</t>
+          <t>no_trust</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Healthcare Professional</t>
+          <t>No Trust</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>no_trust</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>No Trust</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>moderate</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1165,27 +1165,10 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>extremely_high</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>trust_level_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>extremely_high</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
         <is>
           <t>Extremely High</t>
         </is>
